--- a/Project 1 Data Quality Assessment/validation/sumo_input_do_v3_20260919/outputs/dqr_full_period/DQR_full_period_SUMO_audit.xlsx
+++ b/Project 1 Data Quality Assessment/validation/sumo_input_do_v3_20260919/outputs/dqr_full_period/DQR_full_period_SUMO_audit.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PeriodSummary" sheetId="1" r:id="R5d619a9af2344d52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActionSummary" sheetId="2" r:id="R6edaa689773444f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChannelSummary" sheetId="3" r:id="R4ee5916239e74551"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WindowRanking" sheetId="4" r:id="Rb3253b3cc82d41bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SelectedWindows" sheetId="5" r:id="Raccf378d117f4321"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract" sheetId="6" r:id="R45b81ea90e7b42b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PeriodSummary" sheetId="1" r:id="R6cc6cd0e81e846bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActionSummary" sheetId="2" r:id="R9fef88631d824dd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChannelSummary" sheetId="3" r:id="R162277a446be4610"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WindowRanking" sheetId="4" r:id="Ra028193572014373"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SelectedWindows" sheetId="5" r:id="R46dd7562d5ec4e14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contract" sheetId="6" r:id="R674d11534b764e4b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2169,13 +2169,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M2" s="7" t="n">
-        <x:v>81.8700396825</x:v>
+        <x:v>87.3759920635</x:v>
       </x:c>
       <x:c r="N2" s="7" t="n">
-        <x:v>68.3531746032</x:v>
+        <x:v>70.5357142857</x:v>
       </x:c>
       <x:c r="O2" s="7" t="n">
-        <x:v>68.3531746032</x:v>
+        <x:v>70.5357142857</x:v>
       </x:c>
       <x:c r="P2" s="7" t="n">
         <x:v>73.2142857143</x:v>
@@ -2190,7 +2190,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="T2" s="6" t="n">
-        <x:v>343</x:v>
+        <x:v>345</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
@@ -2231,13 +2231,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M3" s="7" t="n">
-        <x:v>75.248015873</x:v>
+        <x:v>80.753968254</x:v>
       </x:c>
       <x:c r="N3" s="7" t="n">
-        <x:v>62.9216269841</x:v>
+        <x:v>65.1041666667</x:v>
       </x:c>
       <x:c r="O3" s="7" t="n">
-        <x:v>62.9216269841</x:v>
+        <x:v>65.1041666667</x:v>
       </x:c>
       <x:c r="P3" s="7" t="n">
         <x:v>73.2142857143</x:v>
@@ -2252,7 +2252,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="T3" s="6" t="n">
-        <x:v>347</x:v>
+        <x:v>348</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
@@ -2293,13 +2293,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M4" s="7" t="n">
-        <x:v>79.8859126984</x:v>
+        <x:v>86.1607142857</x:v>
       </x:c>
       <x:c r="N4" s="7" t="n">
-        <x:v>68.0555555556</x:v>
+        <x:v>71.4037698413</x:v>
       </x:c>
       <x:c r="O4" s="7" t="n">
-        <x:v>68.0555555556</x:v>
+        <x:v>71.4037698413</x:v>
       </x:c>
       <x:c r="P4" s="7" t="n">
         <x:v>75.2976190476</x:v>
@@ -2314,7 +2314,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="T4" s="6" t="n">
-        <x:v>345</x:v>
+        <x:v>343</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
@@ -2355,13 +2355,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M5" s="7" t="n">
-        <x:v>77.5049603175</x:v>
+        <x:v>83.7797619048</x:v>
       </x:c>
       <x:c r="N5" s="7" t="n">
-        <x:v>65.9722222222</x:v>
+        <x:v>69.3204365079</x:v>
       </x:c>
       <x:c r="O5" s="7" t="n">
-        <x:v>65.9722222222</x:v>
+        <x:v>69.3204365079</x:v>
       </x:c>
       <x:c r="P5" s="7" t="n">
         <x:v>74.7023809524</x:v>
@@ -2417,13 +2417,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M6" s="7" t="n">
-        <x:v>73.9087301587</x:v>
+        <x:v>80.2083333333</x:v>
       </x:c>
       <x:c r="N6" s="7" t="n">
-        <x:v>62.3759920635</x:v>
+        <x:v>65.7490079365</x:v>
       </x:c>
       <x:c r="O6" s="7" t="n">
-        <x:v>62.3759920635</x:v>
+        <x:v>65.7490079365</x:v>
       </x:c>
       <x:c r="P6" s="7" t="n">
         <x:v>75.5952380952</x:v>
@@ -2438,7 +2438,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="T6" s="6" t="n">
-        <x:v>348</x:v>
+        <x:v>347</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
@@ -2479,13 +2479,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M7" s="7" t="n">
-        <x:v>88.5416666667</x:v>
+        <x:v>94.0476190476</x:v>
       </x:c>
       <x:c r="N7" s="7" t="n">
-        <x:v>75.4712301587</x:v>
+        <x:v>77.6537698413</x:v>
       </x:c>
       <x:c r="O7" s="7" t="n">
-        <x:v>75.4712301587</x:v>
+        <x:v>77.6537698413</x:v>
       </x:c>
       <x:c r="P7" s="7" t="n">
         <x:v>72.0238095238</x:v>
@@ -2500,7 +2500,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="T7" s="6" t="n">
-        <x:v>328</x:v>
+        <x:v>329</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="22" customHeight="1">
@@ -2541,13 +2541,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M8" s="7" t="n">
-        <x:v>81.0763888889</x:v>
+        <x:v>86.1607142857</x:v>
       </x:c>
       <x:c r="N8" s="7" t="n">
-        <x:v>70.4861111111</x:v>
+        <x:v>74.3799603175</x:v>
       </x:c>
       <x:c r="O8" s="7" t="n">
-        <x:v>70.4861111111</x:v>
+        <x:v>74.3799603175</x:v>
       </x:c>
       <x:c r="P8" s="7" t="n">
         <x:v>77.380952381</x:v>
@@ -2562,7 +2562,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="T8" s="6" t="n">
-        <x:v>335</x:v>
+        <x:v>341</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="22" customHeight="1">
@@ -2603,13 +2603,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M9" s="7" t="n">
-        <x:v>79.2410714286</x:v>
+        <x:v>85.5158730159</x:v>
       </x:c>
       <x:c r="N9" s="7" t="n">
-        <x:v>70.4365079365</x:v>
+        <x:v>76.1160714286</x:v>
       </x:c>
       <x:c r="O9" s="7" t="n">
-        <x:v>70.4365079365</x:v>
+        <x:v>76.1160714286</x:v>
       </x:c>
       <x:c r="P9" s="7" t="n">
         <x:v>77.0833333333</x:v>
@@ -2624,7 +2624,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="T9" s="6" t="n">
-        <x:v>336</x:v>
+        <x:v>331</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
@@ -2665,13 +2665,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M10" s="7" t="n">
-        <x:v>78.0009920635</x:v>
+        <x:v>83.7797619048</x:v>
       </x:c>
       <x:c r="N10" s="7" t="n">
-        <x:v>69.7172619048</x:v>
+        <x:v>74.9503968254</x:v>
       </x:c>
       <x:c r="O10" s="7" t="n">
-        <x:v>69.7172619048</x:v>
+        <x:v>74.9503968254</x:v>
       </x:c>
       <x:c r="P10" s="7" t="n">
         <x:v>78.869047619</x:v>
@@ -2686,7 +2686,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="T10" s="6" t="n">
-        <x:v>339</x:v>
+        <x:v>334</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="22" customHeight="1">
@@ -2727,13 +2727,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M11" s="7" t="n">
-        <x:v>76.2152777778</x:v>
+        <x:v>81.994047619</x:v>
       </x:c>
       <x:c r="N11" s="7" t="n">
-        <x:v>68.2291666667</x:v>
+        <x:v>73.4623015873</x:v>
       </x:c>
       <x:c r="O11" s="7" t="n">
-        <x:v>68.2291666667</x:v>
+        <x:v>73.4623015873</x:v>
       </x:c>
       <x:c r="P11" s="7" t="n">
         <x:v>77.0833333333</x:v>
@@ -2748,7 +2748,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="T11" s="6" t="n">
-        <x:v>344</x:v>
+        <x:v>342</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
@@ -2789,13 +2789,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M12" s="7" t="n">
-        <x:v>88.5416666667</x:v>
+        <x:v>94.0476190476</x:v>
       </x:c>
       <x:c r="N12" s="7" t="n">
-        <x:v>79.6378968254</x:v>
+        <x:v>81.8204365079</x:v>
       </x:c>
       <x:c r="O12" s="7" t="n">
-        <x:v>79.6378968254</x:v>
+        <x:v>81.8204365079</x:v>
       </x:c>
       <x:c r="P12" s="7" t="n">
         <x:v>72.3214285714</x:v>
@@ -2851,13 +2851,13 @@
         <x:v>93.0307539683</x:v>
       </x:c>
       <x:c r="M13" s="7" t="n">
-        <x:v>91.4186507937</x:v>
+        <x:v>94.0476190476</x:v>
       </x:c>
       <x:c r="N13" s="7" t="n">
-        <x:v>87.6240079365</x:v>
+        <x:v>88.1200396825</x:v>
       </x:c>
       <x:c r="O13" s="7" t="n">
-        <x:v>80.8035714286</x:v>
+        <x:v>81.2996031746</x:v>
       </x:c>
       <x:c r="P13" s="7" t="n">
         <x:v>76.1904761905</x:v>
@@ -2872,7 +2872,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="T13" s="6" t="n">
-        <x:v>323</x:v>
+        <x:v>326</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -2913,13 +2913,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M14" s="7" t="n">
-        <x:v>89.0376984127</x:v>
+        <x:v>94.0476190476</x:v>
       </x:c>
       <x:c r="N14" s="7" t="n">
-        <x:v>80.3571428571</x:v>
+        <x:v>82.0436507937</x:v>
       </x:c>
       <x:c r="O14" s="7" t="n">
-        <x:v>80.3571428571</x:v>
+        <x:v>82.0436507937</x:v>
       </x:c>
       <x:c r="P14" s="7" t="n">
         <x:v>72.9166666667</x:v>
@@ -2975,13 +2975,13 @@
         <x:v>88.0952380952</x:v>
       </x:c>
       <x:c r="M15" s="7" t="n">
-        <x:v>99.9503968254</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="N15" s="7" t="n">
-        <x:v>99.9503968254</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="O15" s="7" t="n">
-        <x:v>88.0456349206</x:v>
+        <x:v>88.0952380952</x:v>
       </x:c>
       <x:c r="P15" s="7" t="n">
         <x:v>64.5833333333</x:v>
@@ -2996,7 +2996,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="T15" s="6" t="n">
-        <x:v>262</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
@@ -3037,13 +3037,13 @@
         <x:v>88.0952380952</x:v>
       </x:c>
       <x:c r="M16" s="7" t="n">
-        <x:v>99.9503968254</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="N16" s="7" t="n">
-        <x:v>99.9503968254</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="O16" s="7" t="n">
-        <x:v>88.0456349206</x:v>
+        <x:v>88.0952380952</x:v>
       </x:c>
       <x:c r="P16" s="7" t="n">
         <x:v>63.3928571429</x:v>
@@ -3058,7 +3058,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="T16" s="6" t="n">
-        <x:v>262</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="22" customHeight="1">
@@ -3120,7 +3120,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="T17" s="6" t="n">
-        <x:v>261</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
@@ -3161,13 +3161,13 @@
         <x:v>88.0952380952</x:v>
       </x:c>
       <x:c r="M18" s="7" t="n">
-        <x:v>99.255952381</x:v>
+        <x:v>99.2807539683</x:v>
       </x:c>
       <x:c r="N18" s="7" t="n">
-        <x:v>99.255952381</x:v>
+        <x:v>99.2807539683</x:v>
       </x:c>
       <x:c r="O18" s="7" t="n">
-        <x:v>87.3511904762</x:v>
+        <x:v>87.3759920635</x:v>
       </x:c>
       <x:c r="P18" s="7" t="n">
         <x:v>61.6071428571</x:v>
@@ -3182,7 +3182,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="T18" s="6" t="n">
-        <x:v>267</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="22" customHeight="1">
@@ -3223,13 +3223,13 @@
         <x:v>88.0952380952</x:v>
       </x:c>
       <x:c r="M19" s="7" t="n">
-        <x:v>99.255952381</x:v>
+        <x:v>99.2807539683</x:v>
       </x:c>
       <x:c r="N19" s="7" t="n">
-        <x:v>99.255952381</x:v>
+        <x:v>99.2807539683</x:v>
       </x:c>
       <x:c r="O19" s="7" t="n">
-        <x:v>87.3511904762</x:v>
+        <x:v>87.3759920635</x:v>
       </x:c>
       <x:c r="P19" s="7" t="n">
         <x:v>61.3095238095</x:v>
@@ -3244,7 +3244,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="T19" s="6" t="n">
-        <x:v>267</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
@@ -3285,13 +3285,13 @@
         <x:v>88.0952380952</x:v>
       </x:c>
       <x:c r="M20" s="7" t="n">
-        <x:v>99.255952381</x:v>
+        <x:v>99.2807539683</x:v>
       </x:c>
       <x:c r="N20" s="7" t="n">
-        <x:v>99.255952381</x:v>
+        <x:v>99.2807539683</x:v>
       </x:c>
       <x:c r="O20" s="7" t="n">
-        <x:v>87.3511904762</x:v>
+        <x:v>87.3759920635</x:v>
       </x:c>
       <x:c r="P20" s="7" t="n">
         <x:v>59.2261904762</x:v>
@@ -3306,7 +3306,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="T20" s="6" t="n">
-        <x:v>267</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="22" customHeight="1">
@@ -3347,13 +3347,13 @@
         <x:v>88.0952380952</x:v>
       </x:c>
       <x:c r="M21" s="7" t="n">
-        <x:v>99.255952381</x:v>
+        <x:v>99.2807539683</x:v>
       </x:c>
       <x:c r="N21" s="7" t="n">
-        <x:v>99.255952381</x:v>
+        <x:v>99.2807539683</x:v>
       </x:c>
       <x:c r="O21" s="7" t="n">
-        <x:v>87.3511904762</x:v>
+        <x:v>87.3759920635</x:v>
       </x:c>
       <x:c r="P21" s="7" t="n">
         <x:v>53.869047619</x:v>
@@ -3368,7 +3368,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="T21" s="6" t="n">
-        <x:v>267</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
@@ -3409,13 +3409,13 @@
         <x:v>88.0952380952</x:v>
       </x:c>
       <x:c r="M22" s="7" t="n">
-        <x:v>99.255952381</x:v>
+        <x:v>99.2807539683</x:v>
       </x:c>
       <x:c r="N22" s="7" t="n">
-        <x:v>99.255952381</x:v>
+        <x:v>99.2807539683</x:v>
       </x:c>
       <x:c r="O22" s="7" t="n">
-        <x:v>87.3511904762</x:v>
+        <x:v>87.3759920635</x:v>
       </x:c>
       <x:c r="P22" s="7" t="n">
         <x:v>49.1071428571</x:v>
@@ -3430,7 +3430,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="T22" s="6" t="n">
-        <x:v>267</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="22" customHeight="1">
@@ -3471,13 +3471,13 @@
         <x:v>88.0952380952</x:v>
       </x:c>
       <x:c r="M23" s="7" t="n">
-        <x:v>99.255952381</x:v>
+        <x:v>99.2807539683</x:v>
       </x:c>
       <x:c r="N23" s="7" t="n">
-        <x:v>99.255952381</x:v>
+        <x:v>99.2807539683</x:v>
       </x:c>
       <x:c r="O23" s="7" t="n">
-        <x:v>87.3511904762</x:v>
+        <x:v>87.3759920635</x:v>
       </x:c>
       <x:c r="P23" s="7" t="n">
         <x:v>48.2142857143</x:v>
@@ -3492,7 +3492,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="T23" s="6" t="n">
-        <x:v>267</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
@@ -3533,13 +3533,13 @@
         <x:v>88.0952380952</x:v>
       </x:c>
       <x:c r="M24" s="7" t="n">
-        <x:v>99.255952381</x:v>
+        <x:v>99.2807539683</x:v>
       </x:c>
       <x:c r="N24" s="7" t="n">
-        <x:v>99.255952381</x:v>
+        <x:v>99.2807539683</x:v>
       </x:c>
       <x:c r="O24" s="7" t="n">
-        <x:v>87.3511904762</x:v>
+        <x:v>87.3759920635</x:v>
       </x:c>
       <x:c r="P24" s="7" t="n">
         <x:v>46.130952381</x:v>
@@ -3554,7 +3554,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="T24" s="6" t="n">
-        <x:v>267</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="22" customHeight="1">
@@ -3595,13 +3595,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M25" s="7" t="n">
-        <x:v>78.0009920635</x:v>
+        <x:v>83.7797619048</x:v>
       </x:c>
       <x:c r="N25" s="7" t="n">
-        <x:v>70.3621031746</x:v>
+        <x:v>76.1408730159</x:v>
       </x:c>
       <x:c r="O25" s="7" t="n">
-        <x:v>70.3621031746</x:v>
+        <x:v>76.1408730159</x:v>
       </x:c>
       <x:c r="P25" s="7" t="n">
         <x:v>77.0833333333</x:v>
@@ -3616,7 +3616,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="T25" s="6" t="n">
-        <x:v>337</x:v>
+        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
@@ -3657,13 +3657,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M26" s="7" t="n">
-        <x:v>89.0376984127</x:v>
+        <x:v>94.0476190476</x:v>
       </x:c>
       <x:c r="N26" s="7" t="n">
-        <x:v>80.9027777778</x:v>
+        <x:v>82.5892857143</x:v>
       </x:c>
       <x:c r="O26" s="7" t="n">
-        <x:v>80.9027777778</x:v>
+        <x:v>82.5892857143</x:v>
       </x:c>
       <x:c r="P26" s="7" t="n">
         <x:v>72.0238095238</x:v>
@@ -3678,7 +3678,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="T26" s="6" t="n">
-        <x:v>322</x:v>
+        <x:v>314</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="22" customHeight="1">
@@ -3719,13 +3719,13 @@
         <x:v>85.7886904762</x:v>
       </x:c>
       <x:c r="M27" s="7" t="n">
+        <x:v>96.4533730159</x:v>
+      </x:c>
+      <x:c r="N27" s="7" t="n">
         <x:v>96.378968254</x:v>
       </x:c>
-      <x:c r="N27" s="7" t="n">
-        <x:v>96.3541666667</x:v>
-      </x:c>
       <x:c r="O27" s="7" t="n">
-        <x:v>85.0446428571</x:v>
+        <x:v>85.0694444444</x:v>
       </x:c>
       <x:c r="P27" s="7" t="n">
         <x:v>44.6428571429</x:v>
@@ -3740,7 +3740,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="T27" s="6" t="n">
-        <x:v>287</x:v>
+        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
@@ -3781,13 +3781,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M28" s="7" t="n">
-        <x:v>75.6200396825</x:v>
+        <x:v>81.994047619</x:v>
       </x:c>
       <x:c r="N28" s="7" t="n">
-        <x:v>68.8244047619</x:v>
+        <x:v>74.6527777778</x:v>
       </x:c>
       <x:c r="O28" s="7" t="n">
-        <x:v>68.8244047619</x:v>
+        <x:v>74.6527777778</x:v>
       </x:c>
       <x:c r="P28" s="7" t="n">
         <x:v>78.2738095238</x:v>
@@ -3802,7 +3802,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="T28" s="6" t="n">
-        <x:v>342</x:v>
+        <x:v>336</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="22" customHeight="1">
@@ -3843,13 +3843,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M29" s="7" t="n">
-        <x:v>75.6200396825</x:v>
+        <x:v>81.994047619</x:v>
       </x:c>
       <x:c r="N29" s="7" t="n">
-        <x:v>69.4196428571</x:v>
+        <x:v>75.248015873</x:v>
       </x:c>
       <x:c r="O29" s="7" t="n">
-        <x:v>69.4196428571</x:v>
+        <x:v>75.248015873</x:v>
       </x:c>
       <x:c r="P29" s="7" t="n">
         <x:v>79.4642857143</x:v>
@@ -3864,7 +3864,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="T29" s="6" t="n">
-        <x:v>340</x:v>
+        <x:v>333</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
@@ -3905,13 +3905,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M30" s="7" t="n">
-        <x:v>76.2400793651</x:v>
+        <x:v>81.994047619</x:v>
       </x:c>
       <x:c r="N30" s="7" t="n">
-        <x:v>70.3373015873</x:v>
+        <x:v>75.5456349206</x:v>
       </x:c>
       <x:c r="O30" s="7" t="n">
-        <x:v>70.3373015873</x:v>
+        <x:v>75.5456349206</x:v>
       </x:c>
       <x:c r="P30" s="7" t="n">
         <x:v>79.7619047619</x:v>
@@ -3926,7 +3926,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="T30" s="6" t="n">
-        <x:v>338</x:v>
+        <x:v>332</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="22" customHeight="1">
@@ -3967,13 +3967,13 @@
         <x:v>99.9503968254</x:v>
       </x:c>
       <x:c r="M31" s="7" t="n">
-        <x:v>89.0376984127</x:v>
+        <x:v>94.0476190476</x:v>
       </x:c>
       <x:c r="N31" s="7" t="n">
-        <x:v>81.9692460317</x:v>
+        <x:v>83.6557539683</x:v>
       </x:c>
       <x:c r="O31" s="7" t="n">
-        <x:v>81.9692460317</x:v>
+        <x:v>83.6557539683</x:v>
       </x:c>
       <x:c r="P31" s="7" t="n">
         <x:v>70.2380952381</x:v>
@@ -3988,7 +3988,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="T31" s="6" t="n">
-        <x:v>309</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
@@ -4029,13 +4029,13 @@
         <x:v>99.9255952381</x:v>
       </x:c>
       <x:c r="M32" s="7" t="n">
-        <x:v>89.0376984127</x:v>
+        <x:v>94.0476190476</x:v>
       </x:c>
       <x:c r="N32" s="7" t="n">
-        <x:v>82.1428571429</x:v>
+        <x:v>83.8293650794</x:v>
       </x:c>
       <x:c r="O32" s="7" t="n">
-        <x:v>82.1428571429</x:v>
+        <x:v>83.8293650794</x:v>
       </x:c>
       <x:c r="P32" s="7" t="n">
         <x:v>71.130952381</x:v>
@@ -4050,7 +4050,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T32" s="6" t="n">
-        <x:v>306</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="22" customHeight="1">
@@ -4091,13 +4091,13 @@
         <x:v>99.8759920635</x:v>
       </x:c>
       <x:c r="M33" s="7" t="n">
-        <x:v>90.2281746032</x:v>
+        <x:v>94.0476190476</x:v>
       </x:c>
       <x:c r="N33" s="7" t="n">
-        <x:v>83.2589285714</x:v>
+        <x:v>83.7549603175</x:v>
       </x:c>
       <x:c r="O33" s="7" t="n">
-        <x:v>83.2341269841</x:v>
+        <x:v>83.7301587302</x:v>
       </x:c>
       <x:c r="P33" s="7" t="n">
         <x:v>72.9166666667</x:v>
@@ -4112,7 +4112,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T33" s="6" t="n">
-        <x:v>298</x:v>
+        <x:v>309</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
@@ -4153,13 +4153,13 @@
         <x:v>92.683531746</x:v>
       </x:c>
       <x:c r="M34" s="7" t="n">
-        <x:v>91.3938492063</x:v>
+        <x:v>92.7579365079</x:v>
       </x:c>
       <x:c r="N34" s="7" t="n">
-        <x:v>88.814484127</x:v>
+        <x:v>89.7817460317</x:v>
       </x:c>
       <x:c r="O34" s="7" t="n">
-        <x:v>81.6716269841</x:v>
+        <x:v>82.7876984127</x:v>
       </x:c>
       <x:c r="P34" s="7" t="n">
         <x:v>75.8928571429</x:v>
@@ -4174,7 +4174,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="T34" s="6" t="n">
-        <x:v>321</x:v>
+        <x:v>311</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="22" customHeight="1">
@@ -4215,13 +4215,13 @@
         <x:v>92.6587301587</x:v>
       </x:c>
       <x:c r="M35" s="7" t="n">
-        <x:v>93.7748015873</x:v>
+        <x:v>95.1388888889</x:v>
       </x:c>
       <x:c r="N35" s="7" t="n">
-        <x:v>91.1458333333</x:v>
+        <x:v>92.1130952381</x:v>
       </x:c>
       <x:c r="O35" s="7" t="n">
-        <x:v>84.0029761905</x:v>
+        <x:v>85.119047619</x:v>
       </x:c>
       <x:c r="P35" s="7" t="n">
         <x:v>77.0833333333</x:v>
@@ -4236,7 +4236,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="T35" s="6" t="n">
-        <x:v>293</x:v>
+        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
@@ -4277,13 +4277,13 @@
         <x:v>92.6587301587</x:v>
       </x:c>
       <x:c r="M36" s="7" t="n">
-        <x:v>97.371031746</x:v>
+        <x:v>98.7103174603</x:v>
       </x:c>
       <x:c r="N36" s="7" t="n">
-        <x:v>94.7420634921</x:v>
+        <x:v>95.6845238095</x:v>
       </x:c>
       <x:c r="O36" s="7" t="n">
-        <x:v>87.5992063492</x:v>
+        <x:v>88.6904761905</x:v>
       </x:c>
       <x:c r="P36" s="7" t="n">
         <x:v>75.5952380952</x:v>
@@ -4298,7 +4298,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="T36" s="6" t="n">
-        <x:v>264</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="22" customHeight="1">
@@ -4339,13 +4339,13 @@
         <x:v>88.1448412698</x:v>
       </x:c>
       <x:c r="M37" s="7" t="n">
-        <x:v>96.378968254</x:v>
+        <x:v>96.4533730159</x:v>
       </x:c>
       <x:c r="N37" s="7" t="n">
-        <x:v>96.3293650794</x:v>
+        <x:v>96.3541666667</x:v>
       </x:c>
       <x:c r="O37" s="7" t="n">
-        <x:v>87.4007936508</x:v>
+        <x:v>87.4255952381</x:v>
       </x:c>
       <x:c r="P37" s="7" t="n">
         <x:v>40.7738095238</x:v>
@@ -4360,7 +4360,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="T37" s="6" t="n">
-        <x:v>266</x:v>
+        <x:v>273</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="22" customHeight="1">
@@ -4401,13 +4401,13 @@
         <x:v>98.9831349206</x:v>
       </x:c>
       <x:c r="M38" s="7" t="n">
-        <x:v>90.8234126984</x:v>
+        <x:v>94.0476190476</x:v>
       </x:c>
       <x:c r="N38" s="7" t="n">
-        <x:v>85.2678571429</x:v>
+        <x:v>85.7638888889</x:v>
       </x:c>
       <x:c r="O38" s="7" t="n">
-        <x:v>84.375</x:v>
+        <x:v>84.871031746</x:v>
       </x:c>
       <x:c r="P38" s="7" t="n">
         <x:v>74.4047619048</x:v>
@@ -4422,7 +4422,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="T38" s="6" t="n">
-        <x:v>291</x:v>
+        <x:v>305</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="22" customHeight="1">
@@ -4463,13 +4463,13 @@
         <x:v>92.6587301587</x:v>
       </x:c>
       <x:c r="M39" s="7" t="n">
-        <x:v>96.5277777778</x:v>
+        <x:v>96.9990079365</x:v>
       </x:c>
       <x:c r="N39" s="7" t="n">
-        <x:v>94.6676587302</x:v>
+        <x:v>95.1636904762</x:v>
       </x:c>
       <x:c r="O39" s="7" t="n">
-        <x:v>87.5248015873</x:v>
+        <x:v>88.1696428571</x:v>
       </x:c>
       <x:c r="P39" s="7" t="n">
         <x:v>76.1904761905</x:v>
@@ -4484,7 +4484,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="T39" s="6" t="n">
-        <x:v>265</x:v>
+        <x:v>267</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="22" customHeight="1">
@@ -4525,13 +4525,13 @@
         <x:v>91.6666666667</x:v>
       </x:c>
       <x:c r="M40" s="7" t="n">
-        <x:v>99.9503968254</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="N40" s="7" t="n">
-        <x:v>99.9503968254</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="O40" s="7" t="n">
-        <x:v>91.6170634921</x:v>
+        <x:v>91.6666666667</x:v>
       </x:c>
       <x:c r="P40" s="7" t="n">
         <x:v>67.5595238095</x:v>
@@ -4546,7 +4546,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="T40" s="6" t="n">
-        <x:v>242</x:v>
+        <x:v>249</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="22" customHeight="1">
@@ -4587,13 +4587,13 @@
         <x:v>92.3363095238</x:v>
       </x:c>
       <x:c r="M41" s="7" t="n">
-        <x:v>96.9494047619</x:v>
+        <x:v>96.9990079365</x:v>
       </x:c>
       <x:c r="N41" s="7" t="n">
-        <x:v>96.2053571429</x:v>
+        <x:v>96.2797619048</x:v>
       </x:c>
       <x:c r="O41" s="7" t="n">
-        <x:v>88.7648809524</x:v>
+        <x:v>88.9880952381</x:v>
       </x:c>
       <x:c r="P41" s="7" t="n">
         <x:v>84.2261904762</x:v>
@@ -4608,7 +4608,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="T41" s="6" t="n">
-        <x:v>255</x:v>
+        <x:v>265</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="22" customHeight="1">
@@ -4649,13 +4649,13 @@
         <x:v>92.3611111111</x:v>
       </x:c>
       <x:c r="M42" s="7" t="n">
-        <x:v>96.9494047619</x:v>
+        <x:v>96.9990079365</x:v>
       </x:c>
       <x:c r="N42" s="7" t="n">
-        <x:v>96.2797619048</x:v>
+        <x:v>96.3541666667</x:v>
       </x:c>
       <x:c r="O42" s="7" t="n">
-        <x:v>88.8392857143</x:v>
+        <x:v>89.0625</x:v>
       </x:c>
       <x:c r="P42" s="7" t="n">
         <x:v>85.4166666667</x:v>
@@ -4670,7 +4670,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="T42" s="6" t="n">
-        <x:v>254</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="22" customHeight="1">
@@ -4711,13 +4711,13 @@
         <x:v>92.4107142857</x:v>
       </x:c>
       <x:c r="M43" s="7" t="n">
-        <x:v>96.9494047619</x:v>
+        <x:v>96.9990079365</x:v>
       </x:c>
       <x:c r="N43" s="7" t="n">
-        <x:v>96.3541666667</x:v>
+        <x:v>96.4285714286</x:v>
       </x:c>
       <x:c r="O43" s="7" t="n">
-        <x:v>88.9384920635</x:v>
+        <x:v>89.1617063492</x:v>
       </x:c>
       <x:c r="P43" s="7" t="n">
         <x:v>86.9047619048</x:v>
@@ -4732,7 +4732,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="T43" s="6" t="n">
-        <x:v>253</x:v>
+        <x:v>263</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="22" customHeight="1">
@@ -4773,13 +4773,13 @@
         <x:v>92.6587301587</x:v>
       </x:c>
       <x:c r="M44" s="7" t="n">
-        <x:v>96.5277777778</x:v>
+        <x:v>96.9990079365</x:v>
       </x:c>
       <x:c r="N44" s="7" t="n">
-        <x:v>95.7837301587</x:v>
+        <x:v>96.2797619048</x:v>
       </x:c>
       <x:c r="O44" s="7" t="n">
-        <x:v>88.6408730159</x:v>
+        <x:v>89.2857142857</x:v>
       </x:c>
       <x:c r="P44" s="7" t="n">
         <x:v>77.380952381</x:v>
@@ -4794,7 +4794,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="T44" s="6" t="n">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="22" customHeight="1">
@@ -4835,13 +4835,13 @@
         <x:v>92.6587301587</x:v>
       </x:c>
       <x:c r="M45" s="7" t="n">
-        <x:v>96.5277777778</x:v>
+        <x:v>96.9990079365</x:v>
       </x:c>
       <x:c r="N45" s="7" t="n">
-        <x:v>95.7341269841</x:v>
+        <x:v>96.2301587302</x:v>
       </x:c>
       <x:c r="O45" s="7" t="n">
-        <x:v>88.5912698413</x:v>
+        <x:v>89.2361111111</x:v>
       </x:c>
       <x:c r="P45" s="7" t="n">
         <x:v>78.869047619</x:v>
@@ -4897,13 +4897,13 @@
         <x:v>92.6587301587</x:v>
       </x:c>
       <x:c r="M46" s="7" t="n">
-        <x:v>96.5277777778</x:v>
+        <x:v>96.9990079365</x:v>
       </x:c>
       <x:c r="N46" s="7" t="n">
-        <x:v>95.7341269841</x:v>
+        <x:v>96.2301587302</x:v>
       </x:c>
       <x:c r="O46" s="7" t="n">
-        <x:v>88.5912698413</x:v>
+        <x:v>89.2361111111</x:v>
       </x:c>
       <x:c r="P46" s="7" t="n">
         <x:v>79.4642857143</x:v>
@@ -4959,13 +4959,13 @@
         <x:v>92.6339285714</x:v>
       </x:c>
       <x:c r="M47" s="7" t="n">
-        <x:v>96.9494047619</x:v>
+        <x:v>96.9990079365</x:v>
       </x:c>
       <x:c r="N47" s="7" t="n">
-        <x:v>96.1061507937</x:v>
+        <x:v>96.1805555556</x:v>
       </x:c>
       <x:c r="O47" s="7" t="n">
-        <x:v>88.9632936508</x:v>
+        <x:v>89.1865079365</x:v>
       </x:c>
       <x:c r="P47" s="7" t="n">
         <x:v>79.4642857143</x:v>
@@ -4980,7 +4980,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="T47" s="6" t="n">
-        <x:v>251</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="22" customHeight="1">
@@ -5021,13 +5021,13 @@
         <x:v>92.6091269841</x:v>
       </x:c>
       <x:c r="M48" s="7" t="n">
-        <x:v>96.9494047619</x:v>
+        <x:v>96.9990079365</x:v>
       </x:c>
       <x:c r="N48" s="7" t="n">
-        <x:v>96.1061507937</x:v>
+        <x:v>96.1805555556</x:v>
       </x:c>
       <x:c r="O48" s="7" t="n">
-        <x:v>88.9632936508</x:v>
+        <x:v>89.1865079365</x:v>
       </x:c>
       <x:c r="P48" s="7" t="n">
         <x:v>81.5476190476</x:v>
@@ -5042,7 +5042,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="T48" s="6" t="n">
-        <x:v>251</x:v>
+        <x:v>261</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="22" customHeight="1">
@@ -5083,13 +5083,13 @@
         <x:v>89.9305555556</x:v>
       </x:c>
       <x:c r="M49" s="7" t="n">
-        <x:v>96.378968254</x:v>
+        <x:v>96.4533730159</x:v>
       </x:c>
       <x:c r="N49" s="7" t="n">
-        <x:v>96.3293650794</x:v>
+        <x:v>96.3541666667</x:v>
       </x:c>
       <x:c r="O49" s="7" t="n">
-        <x:v>89.1865079365</x:v>
+        <x:v>89.2113095238</x:v>
       </x:c>
       <x:c r="P49" s="7" t="n">
         <x:v>37.7976190476</x:v>
@@ -5104,7 +5104,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="T49" s="6" t="n">
-        <x:v>250</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="22" customHeight="1">
@@ -5145,13 +5145,13 @@
         <x:v>93.3035714286</x:v>
       </x:c>
       <x:c r="M50" s="7" t="n">
-        <x:v>96.9494047619</x:v>
+        <x:v>96.9990079365</x:v>
       </x:c>
       <x:c r="N50" s="7" t="n">
-        <x:v>96.4285714286</x:v>
+        <x:v>96.5029761905</x:v>
       </x:c>
       <x:c r="O50" s="7" t="n">
-        <x:v>89.880952381</x:v>
+        <x:v>90.1041666667</x:v>
       </x:c>
       <x:c r="P50" s="7" t="n">
         <x:v>88.0952380952</x:v>
@@ -5166,7 +5166,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="T50" s="6" t="n">
-        <x:v>248</x:v>
+        <x:v>253</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="22" customHeight="1">
@@ -5207,13 +5207,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M51" s="7" t="n">
-        <x:v>75</x:v>
+        <x:v>81.994047619</x:v>
       </x:c>
       <x:c r="N51" s="7" t="n">
-        <x:v>73.2638888889</x:v>
+        <x:v>79.4146825397</x:v>
       </x:c>
       <x:c r="O51" s="7" t="n">
-        <x:v>73.2638888889</x:v>
+        <x:v>79.4146825397</x:v>
       </x:c>
       <x:c r="P51" s="7" t="n">
         <x:v>79.1666666667</x:v>
@@ -5228,7 +5228,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="T51" s="6" t="n">
-        <x:v>329</x:v>
+        <x:v>328</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="22" customHeight="1">
@@ -5269,13 +5269,13 @@
         <x:v>95.2380952381</x:v>
       </x:c>
       <x:c r="M52" s="7" t="n">
-        <x:v>99.9503968254</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="N52" s="7" t="n">
-        <x:v>99.9503968254</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="O52" s="7" t="n">
-        <x:v>95.1884920635</x:v>
+        <x:v>95.2380952381</x:v>
       </x:c>
       <x:c r="P52" s="7" t="n">
         <x:v>69.3452380952</x:v>
@@ -5290,7 +5290,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="T52" s="6" t="n">
-        <x:v>215</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="22" customHeight="1">
@@ -5331,13 +5331,13 @@
         <x:v>93.501984127</x:v>
       </x:c>
       <x:c r="M53" s="7" t="n">
-        <x:v>96.378968254</x:v>
+        <x:v>96.4533730159</x:v>
       </x:c>
       <x:c r="N53" s="7" t="n">
-        <x:v>96.3293650794</x:v>
+        <x:v>96.3541666667</x:v>
       </x:c>
       <x:c r="O53" s="7" t="n">
-        <x:v>92.7579365079</x:v>
+        <x:v>92.7827380952</x:v>
       </x:c>
       <x:c r="P53" s="7" t="n">
         <x:v>32.4404761905</x:v>
@@ -5352,7 +5352,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="T53" s="6" t="n">
-        <x:v>240</x:v>
+        <x:v>243</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="22" customHeight="1">
@@ -5393,13 +5393,13 @@
         <x:v>97.0238095238</x:v>
       </x:c>
       <x:c r="M54" s="7" t="n">
-        <x:v>99.9503968254</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="N54" s="7" t="n">
-        <x:v>99.9503968254</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="O54" s="7" t="n">
-        <x:v>96.9742063492</x:v>
+        <x:v>97.0238095238</x:v>
       </x:c>
       <x:c r="P54" s="7" t="n">
         <x:v>73.5119047619</x:v>
@@ -5414,7 +5414,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="T54" s="6" t="n">
-        <x:v>201</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="22" customHeight="1">
@@ -5455,13 +5455,13 @@
         <x:v>98.0158730159</x:v>
       </x:c>
       <x:c r="M55" s="7" t="n">
-        <x:v>78.0753968254</x:v>
+        <x:v>87.1775793651</x:v>
       </x:c>
       <x:c r="N55" s="7" t="n">
-        <x:v>76.7361111111</x:v>
+        <x:v>84.5238095238</x:v>
       </x:c>
       <x:c r="O55" s="7" t="n">
-        <x:v>76.7361111111</x:v>
+        <x:v>84.5238095238</x:v>
       </x:c>
       <x:c r="P55" s="7" t="n">
         <x:v>74.7023809524</x:v>
@@ -5476,7 +5476,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="T55" s="6" t="n">
-        <x:v>327</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="22" customHeight="1">
@@ -5517,13 +5517,13 @@
         <x:v>98.0158730159</x:v>
       </x:c>
       <x:c r="M56" s="7" t="n">
-        <x:v>86.433531746</x:v>
+        <x:v>94.3452380952</x:v>
       </x:c>
       <x:c r="N56" s="7" t="n">
-        <x:v>85.0942460317</x:v>
+        <x:v>91.691468254</x:v>
       </x:c>
       <x:c r="O56" s="7" t="n">
-        <x:v>85.0942460317</x:v>
+        <x:v>91.691468254</x:v>
       </x:c>
       <x:c r="P56" s="7" t="n">
         <x:v>75.8928571429</x:v>
@@ -5538,7 +5538,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="T56" s="6" t="n">
-        <x:v>285</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="22" customHeight="1">
@@ -5579,13 +5579,13 @@
         <x:v>98.0158730159</x:v>
       </x:c>
       <x:c r="M57" s="7" t="n">
-        <x:v>86.433531746</x:v>
+        <x:v>94.3452380952</x:v>
       </x:c>
       <x:c r="N57" s="7" t="n">
-        <x:v>85.0942460317</x:v>
+        <x:v>91.691468254</x:v>
       </x:c>
       <x:c r="O57" s="7" t="n">
-        <x:v>85.0942460317</x:v>
+        <x:v>91.691468254</x:v>
       </x:c>
       <x:c r="P57" s="7" t="n">
         <x:v>74.1071428571</x:v>
@@ -5600,7 +5600,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="T57" s="6" t="n">
-        <x:v>285</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="22" customHeight="1">
@@ -5641,13 +5641,13 @@
         <x:v>98.0158730159</x:v>
       </x:c>
       <x:c r="M58" s="7" t="n">
-        <x:v>84.6974206349</x:v>
+        <x:v>93.7996031746</x:v>
       </x:c>
       <x:c r="N58" s="7" t="n">
-        <x:v>83.3581349206</x:v>
+        <x:v>91.1458333333</x:v>
       </x:c>
       <x:c r="O58" s="7" t="n">
-        <x:v>83.3581349206</x:v>
+        <x:v>91.1458333333</x:v>
       </x:c>
       <x:c r="P58" s="7" t="n">
         <x:v>74.7023809524</x:v>
@@ -5662,7 +5662,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="T58" s="6" t="n">
-        <x:v>296</x:v>
+        <x:v>251</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="22" customHeight="1">
@@ -5703,13 +5703,13 @@
         <x:v>98.0158730159</x:v>
       </x:c>
       <x:c r="M59" s="7" t="n">
-        <x:v>89.4593253968</x:v>
+        <x:v>94.9900793651</x:v>
       </x:c>
       <x:c r="N59" s="7" t="n">
-        <x:v>88.4176587302</x:v>
+        <x:v>92.6339285714</x:v>
       </x:c>
       <x:c r="O59" s="7" t="n">
-        <x:v>88.4176587302</x:v>
+        <x:v>92.6339285714</x:v>
       </x:c>
       <x:c r="P59" s="7" t="n">
         <x:v>79.1666666667</x:v>
@@ -5724,7 +5724,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="T59" s="6" t="n">
-        <x:v>260</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="22" customHeight="1">
@@ -5765,13 +5765,13 @@
         <x:v>98.0158730159</x:v>
       </x:c>
       <x:c r="M60" s="7" t="n">
-        <x:v>87.0287698413</x:v>
+        <x:v>94.3452380952</x:v>
       </x:c>
       <x:c r="N60" s="7" t="n">
-        <x:v>85.9871031746</x:v>
+        <x:v>91.9890873016</x:v>
       </x:c>
       <x:c r="O60" s="7" t="n">
-        <x:v>85.9871031746</x:v>
+        <x:v>91.9890873016</x:v>
       </x:c>
       <x:c r="P60" s="7" t="n">
         <x:v>76.1904761905</x:v>
@@ -5786,7 +5786,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="T60" s="6" t="n">
-        <x:v>275</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="22" customHeight="1">
@@ -5827,13 +5827,13 @@
         <x:v>98.0158730159</x:v>
       </x:c>
       <x:c r="M61" s="7" t="n">
-        <x:v>86.433531746</x:v>
+        <x:v>94.3452380952</x:v>
       </x:c>
       <x:c r="N61" s="7" t="n">
-        <x:v>85.3918650794</x:v>
+        <x:v>91.9890873016</x:v>
       </x:c>
       <x:c r="O61" s="7" t="n">
-        <x:v>85.3918650794</x:v>
+        <x:v>91.9890873016</x:v>
       </x:c>
       <x:c r="P61" s="7" t="n">
         <x:v>75.8928571429</x:v>
@@ -5848,7 +5848,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="T61" s="6" t="n">
-        <x:v>284</x:v>
+        <x:v>245</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5986,13 +5986,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="M2" s="7" t="n">
-        <x:v>81.8700396825</x:v>
+        <x:v>87.3759920635</x:v>
       </x:c>
       <x:c r="N2" s="7" t="n">
-        <x:v>68.3531746032</x:v>
+        <x:v>70.5357142857</x:v>
       </x:c>
       <x:c r="O2" s="7" t="n">
-        <x:v>68.3531746032</x:v>
+        <x:v>70.5357142857</x:v>
       </x:c>
       <x:c r="P2" s="7" t="n">
         <x:v>73.2142857143</x:v>
@@ -6007,7 +6007,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="T2" s="6" t="n">
-        <x:v>343</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="U2" s="2"/>
     </x:row>
@@ -6049,13 +6049,13 @@
         <x:v>92.6587301587</x:v>
       </x:c>
       <x:c r="M3" s="7" t="n">
-        <x:v>97.371031746</x:v>
+        <x:v>98.7103174603</x:v>
       </x:c>
       <x:c r="N3" s="7" t="n">
-        <x:v>94.7420634921</x:v>
+        <x:v>95.6845238095</x:v>
       </x:c>
       <x:c r="O3" s="7" t="n">
-        <x:v>87.5992063492</x:v>
+        <x:v>88.6904761905</x:v>
       </x:c>
       <x:c r="P3" s="7" t="n">
         <x:v>75.5952380952</x:v>
@@ -6070,7 +6070,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="T3" s="6" t="n">
-        <x:v>264</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="U3" s="2" t="n">
         <x:v>384</x:v>
@@ -6078,10 +6078,10 @@
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
       <x:c r="A4" s="8" t="n">
-        <x:v>45988</x:v>
+        <x:v>45966</x:v>
       </x:c>
       <x:c r="B4" s="8" t="n">
-        <x:v>46002</x:v>
+        <x:v>45980</x:v>
       </x:c>
       <x:c r="C4" s="2" t="str">
         <x:v>retrospective_development</x:v>
@@ -6123,10 +6123,10 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="P4" s="7" t="n">
-        <x:v>84.2261904762</x:v>
+        <x:v>43.1547619048</x:v>
       </x:c>
       <x:c r="Q4" s="7" t="n">
-        <x:v>84.2261904762</x:v>
+        <x:v>43.1547619048</x:v>
       </x:c>
       <x:c r="R4" s="6" t="n">
         <x:v>4032</x:v>
@@ -6235,7 +6235,7 @@
         <x:v>max_contrast_window</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
-        <x:v>{"start": "2025-09-26 00:00:00", "end_exclusive": "2025-10-10 00:00:00", "phase": "retrospective_development", "DO6_quality_excluded_bins": 804, "DO6_quality_excluded_pct_raw_valid": 3.3234126984126986, "ORP_quality_excluded_bins": 0, "ORP_quality_excluded_pct_raw_valid": 0.0, "source_unassessed_bins": 0, "DO6_common_complete_pct": 100.0, "DO6_DQR_complete_pct": 80.05952380952381, "DO8_DQR_complete_pct": 80.05952380952381, "ORP6_DQR_complete_pct": 100.0, "required_process_complete_pct": 81.87003968253968, "joint_DO8_process_complete_pct": 68.35317460317461, "joint_DO8_ORP6_process_complete_pct": 68.35317460317461, "D5_report_available_pct": 73.21428571428571, "full_evidence_pct": 73.21428571428571, "expected_5min_bins": 4032, "contrast_rank": 1, "direct_run_rank": 343}</x:v>
+        <x:v>{"start": "2025-09-26 00:00:00", "end_exclusive": "2025-10-10 00:00:00", "phase": "retrospective_development", "DO6_quality_excluded_bins": 804, "DO6_quality_excluded_pct_raw_valid": 3.3234126984126986, "ORP_quality_excluded_bins": 0, "ORP_quality_excluded_pct_raw_valid": 0.0, "source_unassessed_bins": 0, "DO6_common_complete_pct": 100.0, "DO6_DQR_complete_pct": 80.05952380952381, "DO8_DQR_complete_pct": 80.05952380952381, "ORP6_DQR_complete_pct": 100.0, "required_process_complete_pct": 87.37599206349206, "joint_DO8_process_complete_pct": 70.53571428571429, "joint_DO8_ORP6_process_complete_pct": 70.53571428571429, "D5_report_available_pct": 73.21428571428571, "full_evidence_pct": 73.21428571428571, "expected_5min_bins": 4032, "contrast_rank": 1, "direct_run_rank": 345}</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="32" customHeight="1">
@@ -6243,7 +6243,7 @@
         <x:v>balanced_DO_intervention_window</x:v>
       </x:c>
       <x:c r="B12" s="12" t="str">
-        <x:v>{"start": "2025-10-08 00:00:00", "end_exclusive": "2025-10-22 00:00:00", "phase": "retrospective_development", "DO6_quality_excluded_bins": 96, "DO6_quality_excluded_pct_raw_valid": 0.39713730194845487, "ORP_quality_excluded_bins": 288, "ORP_quality_excluded_pct_raw_valid": 1.1908699966920278, "source_unassessed_bins": 0, "DO6_common_complete_pct": 99.57837301587301, "DO6_DQR_complete_pct": 97.19742063492063, "DO8_DQR_complete_pct": 96.97420634920636, "ORP6_DQR_complete_pct": 92.65873015873017, "required_process_complete_pct": 97.37103174603175, "joint_DO8_process_complete_pct": 94.7420634920635, "joint_DO8_ORP6_process_complete_pct": 87.59920634920636, "D5_report_available_pct": 75.59523809523809, "full_evidence_pct": 75.59523809523809, "expected_5min_bins": 4032, "contrast_rank": 33, "direct_run_rank": 264, "DO_ORP_quality_excluded_bins": 384}</x:v>
+        <x:v>{"start": "2025-10-08 00:00:00", "end_exclusive": "2025-10-22 00:00:00", "phase": "retrospective_development", "DO6_quality_excluded_bins": 96, "DO6_quality_excluded_pct_raw_valid": 0.39713730194845487, "ORP_quality_excluded_bins": 288, "ORP_quality_excluded_pct_raw_valid": 1.1908699966920278, "source_unassessed_bins": 0, "DO6_common_complete_pct": 99.57837301587301, "DO6_DQR_complete_pct": 97.19742063492063, "DO8_DQR_complete_pct": 96.97420634920636, "ORP6_DQR_complete_pct": 92.65873015873017, "required_process_complete_pct": 98.71031746031747, "joint_DO8_process_complete_pct": 95.68452380952381, "joint_DO8_ORP6_process_complete_pct": 88.69047619047619, "D5_report_available_pct": 75.59523809523809, "full_evidence_pct": 75.59523809523809, "expected_5min_bins": 4032, "contrast_rank": 33, "direct_run_rank": 266, "DO_ORP_quality_excluded_bins": 384}</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
@@ -6251,7 +6251,7 @@
         <x:v>best_direct_coverage_window</x:v>
       </x:c>
       <x:c r="B13" s="12" t="str">
-        <x:v>{"start": "2025-11-27 00:00:00", "end_exclusive": "2025-12-11 00:00:00", "phase": "retrospective_development", "DO6_quality_excluded_bins": 0, "DO6_quality_excluded_pct_raw_valid": 0.0, "ORP_quality_excluded_bins": 0, "ORP_quality_excluded_pct_raw_valid": 0.0, "source_unassessed_bins": 0, "DO6_common_complete_pct": 100.0, "DO6_DQR_complete_pct": 100.0, "DO8_DQR_complete_pct": 100.0, "ORP6_DQR_complete_pct": 100.0, "required_process_complete_pct": 100.0, "joint_DO8_process_complete_pct": 100.0, "joint_DO8_ORP6_process_complete_pct": 100.0, "D5_report_available_pct": 84.22619047619048, "full_evidence_pct": 84.22619047619048, "expected_5min_bins": 4032, "contrast_rank": 79, "direct_run_rank": 1}</x:v>
+        <x:v>{"start": "2025-11-05 00:00:00", "end_exclusive": "2025-11-19 00:00:00", "phase": "retrospective_development", "DO6_quality_excluded_bins": 0, "DO6_quality_excluded_pct_raw_valid": 0.0, "ORP_quality_excluded_bins": 0, "ORP_quality_excluded_pct_raw_valid": 0.0, "source_unassessed_bins": 0, "DO6_common_complete_pct": 100.0, "DO6_DQR_complete_pct": 100.0, "DO8_DQR_complete_pct": 100.0, "ORP6_DQR_complete_pct": 100.0, "required_process_complete_pct": 100.0, "joint_DO8_process_complete_pct": 100.0, "joint_DO8_ORP6_process_complete_pct": 100.0, "D5_report_available_pct": 43.154761904761905, "full_evidence_pct": 43.154761904761905, "expected_5min_bins": 4032, "contrast_rank": 79, "direct_run_rank": 1}</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="32" customHeight="1">
